--- a/artfynd/A 49323-2021 artfynd.xlsx
+++ b/artfynd/A 49323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,323 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135131753</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogsängen N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601060</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6558226</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135131765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsängen N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601060</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6558226</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135131755</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107697</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224273</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig ängskovall</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. pratense</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogsängen N om , Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601060</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6558226</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49323-2021 artfynd.xlsx
+++ b/artfynd/A 49323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2988798</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135131753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135131765</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,8 +1256,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135131755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49323-2021 artfynd.xlsx
+++ b/artfynd/A 49323-2021 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>135131753</v>
       </c>
       <c r="B4" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>135131765</v>
       </c>
       <c r="B5" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135131755</v>
       </c>
       <c r="B6" t="n">
-        <v>107697</v>
+        <v>107752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49323-2021 artfynd.xlsx
+++ b/artfynd/A 49323-2021 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>135131753</v>
       </c>
       <c r="B4" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>135131765</v>
       </c>
       <c r="B5" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135131755</v>
       </c>
       <c r="B6" t="n">
-        <v>107752</v>
+        <v>107779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
